--- a/tame_output/ON/bt/strategyON_20240419.xlsx
+++ b/tame_output/ON/bt/strategyON_20240419.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.2%</t>
+          <t>138.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.6%</t>
+          <t>-576.0%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-266.7%</t>
+          <t>-266.9%</t>
         </is>
       </c>
     </row>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781942</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487767</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.742181311543336</v>
+        <v>3.742181311543335</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.140518303703663</v>
+        <v>-4.144755468136263</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.095204298341083</v>
+        <v>1.093509432568043</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5214949482751984</v>

--- a/tame_output/ON/bt/strategyON_20240419.xlsx
+++ b/tame_output/ON/bt/strategyON_20240419.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>118.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.3%</t>
+          <t>138.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.2%</t>
+          <t>788.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-576.0%</t>
+          <t>-559.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-266.9%</t>
+          <t>-260.3%</t>
         </is>
       </c>
     </row>
@@ -46125,10 +46125,10 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.144755468136263</v>
+        <v>-3.981002952839195</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.093509432568043</v>
+        <v>1.15901043868687</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5214949482751984</v>

--- a/tame_output/ON/bt/strategyON_20240419.xlsx
+++ b/tame_output/ON/bt/strategyON_20240419.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.6%</t>
+          <t>781.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-559.7%</t>
+          <t>-561.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-260.3%</t>
+          <t>-261.1%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776675</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.18455424740169</v>
+        <v>-11.34169150085582</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.30844161023119</v>
+        <v>-1.37129651161284</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.476205924133809</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9173124465333</v>
+        <v>-11.07444969998742</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.203379450383205</v>
+        <v>-1.266234351764854</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.476205924133809</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.64150328313281</v>
+        <v>-10.79864053658694</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.093356099996472</v>
+        <v>-1.156211001378121</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.387186615855075</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61754974215685</v>
+        <v>-10.77468699561098</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.083106177460595</v>
+        <v>-1.145961078842244</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.363233074879118</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.35348980383406</v>
+        <v>-10.51062705728818</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9907425182932279</v>
+        <v>-1.053597419674878</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.099173136556322</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.646410180329219</v>
+        <v>-9.803547433783343</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7106977025515944</v>
+        <v>-0.7735526039332439</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.099173136556322</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.606225881963029</v>
+        <v>-9.763363135417153</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6942803593172768</v>
+        <v>-0.7571352606989263</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.058988838190131</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.526156086425225</v>
+        <v>-9.683293339879349</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6628856198813979</v>
+        <v>-0.7257405212630474</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.978919042652327</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.292674864195625</v>
+        <v>-9.449812117649749</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.561568702151706</v>
+        <v>-0.6244236035333555</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.745437820422728</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.112966334051752</v>
+        <v>-9.270103587505876</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4925775004071156</v>
+        <v>-0.5554324017887651</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.688266316260032</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.980690860420864</v>
+        <v>-9.137828113874988</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4442998242077336</v>
+        <v>-0.5071547255893831</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.555990842629146</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.790091185747711</v>
+        <v>-8.947228439201835</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3652448936508357</v>
+        <v>-0.4280997950324852</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.365391167955993</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.54109138706413</v>
+        <v>-8.698228640518254</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2527386329537444</v>
+        <v>-0.3155935343353939</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.365391167955993</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.646681376837234</v>
+        <v>-8.803818630291358</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4229505584622046</v>
+        <v>-0.4858054598438546</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.470981157729098</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.665416278955831</v>
+        <v>-8.822553532409955</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3819001774325574</v>
+        <v>-0.4447550788142069</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.470981157729098</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.517476237548232</v>
+        <v>-8.674613491002356</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4426030835576853</v>
+        <v>-0.5054579849393348</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.45066024182054</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.390583831113162</v>
+        <v>-8.547721084567286</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4005601072371352</v>
+        <v>-0.4634150086187847</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.32376783538547</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.34703542434247</v>
+        <v>-8.504172677796594</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3901013566239517</v>
+        <v>-0.4529562580056012</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.32376783538547</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.104887030888612</v>
+        <v>-8.262024284342736</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2787796448612654</v>
+        <v>-0.3416345462429149</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.32376783538547</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.041657659120265</v>
+        <v>-8.198794912574389</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2589557756947314</v>
+        <v>-0.3218106770763809</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.32376783538547</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.855169966743259</v>
+        <v>-8.012307220197382</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1868626047333524</v>
+        <v>-0.2497175061150014</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.137280143008464</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.834020767839815</v>
+        <v>-7.991158021293939</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1707019469346496</v>
+        <v>-0.2335568483162991</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.11613094410502</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.590255325856371</v>
+        <v>-7.747392579310494</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07741506179422109</v>
+        <v>-0.1402699631758706</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.11613094410502</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.326227258663112</v>
+        <v>-7.483364512117234</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.03032047900309864</v>
+        <v>-0.03253442237855042</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.914265545289067</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.076376864714037</v>
+        <v>-7.233514118168159</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1230027115664307</v>
+        <v>0.06014781018478166</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.914265545289067</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.772809375710058</v>
+        <v>-6.92994662916418</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2480288306886709</v>
+        <v>0.1851739293070218</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.914265545289067</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.699329466858044</v>
+        <v>-6.856466720312167</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2907483002840299</v>
+        <v>0.2278933989023813</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.840785636437053</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.474296467189221</v>
+        <v>-6.631433720643344</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3797819777678564</v>
+        <v>0.3169270763862073</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.61575263676823</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.259662089552815</v>
+        <v>-6.416799343006937</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4703305298767364</v>
+        <v>0.4074756284950873</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.401118259131823</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.993061732578463</v>
+        <v>-6.259661189414186</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5581649314502726</v>
+        <v>0.4515251487159833</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.401118259131823</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.752631235773602</v>
+        <v>-6.019230692609326</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6560802067970943</v>
+        <v>0.5494404240628046</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.160687762326963</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.509840428124157</v>
+        <v>-5.77643988495988</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7571258436916923</v>
+        <v>0.650486060957403</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.160687762326963</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.270235336517068</v>
+        <v>-5.53683479335279</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.853646464251868</v>
+        <v>0.7470066815175791</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.093639814658468</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.027579748093904</v>
+        <v>-5.294179204929627</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9477067708411271</v>
+        <v>0.8410669881068382</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.093639814658468</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145933</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.807558950056894</v>
+        <v>-5.074158406892616</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.037294127066545</v>
+        <v>0.9306543443322566</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.952419969590488</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009945</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.608310320152085</v>
+        <v>-4.874909776987807</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.132887761830292</v>
+        <v>1.026247979096004</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.952419969590488</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.448795216632715</v>
+        <v>-4.715394673468437</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.197839647678342</v>
+        <v>1.091199864944053</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7929048660711181</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.304123071532977</v>
+        <v>-4.5707225283687</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.265796608279677</v>
+        <v>1.159156825545388</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6482327209713807</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.286353612602022</v>
+        <v>-4.552953069437744</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.188244083938781</v>
+        <v>1.081604301204492</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6304632620404251</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.199554114823012</v>
+        <v>-4.466153571658735</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.245364376372951</v>
+        <v>1.138724593638662</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6304632620404251</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.099861500094001</v>
+        <v>-4.366460956929723</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.285313823637968</v>
+        <v>1.178674040903679</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5307706473114133</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.168231686418011</v>
+        <v>-4.434831143253733</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.268972671583066</v>
+        <v>1.162332888848777</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5214949482751984</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.046815256791534</v>
+        <v>-4.313414713627257</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.307975952065547</v>
+        <v>1.201336169331259</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5214949482751984</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.742181311543335</v>
+        <v>3.409196486579662</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981002952839195</v>
+        <v>-4.001716924589848</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.15901043868687</v>
+        <v>1.150724849986609</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5214949482751984</v>

--- a/tame_output/ON/bt/strategyON_20240419.xlsx
+++ b/tame_output/ON/bt/strategyON_20240419.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-55.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.0%</t>
+          <t>117.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.2%</t>
+          <t>138.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>781.4%</t>
+          <t>780.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-561.7%</t>
+          <t>-584.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-261.1%</t>
+          <t>-270.1%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-202.1%</t>
+          <t>-190.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1938"/>
+  <dimension ref="A1:G1939"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776675</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.34169150085582</v>
+        <v>-11.18455424740169</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.37129651161284</v>
+        <v>-1.30844161023119</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.476205924133809</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.07444969998742</v>
+        <v>-10.9173124465333</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.266234351764854</v>
+        <v>-1.203379450383205</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.476205924133809</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.79864053658694</v>
+        <v>-10.64150328313281</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.156211001378121</v>
+        <v>-1.093356099996472</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.387186615855075</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567238</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.77468699561098</v>
+        <v>-10.61754974215685</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.145961078842244</v>
+        <v>-1.083106177460595</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.363233074879118</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.51062705728818</v>
+        <v>-10.35348980383406</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.053597419674878</v>
+        <v>-0.9907425182932279</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.099173136556322</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.803547433783343</v>
+        <v>-9.646410180329219</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7735526039332439</v>
+        <v>-0.7106977025515944</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.099173136556322</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.763363135417153</v>
+        <v>-9.606225881963029</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7571352606989263</v>
+        <v>-0.6942803593172768</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.058988838190131</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.683293339879349</v>
+        <v>-9.526156086425225</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7257405212630474</v>
+        <v>-0.6628856198813979</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.978919042652327</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.449812117649749</v>
+        <v>-9.292674864195625</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6244236035333555</v>
+        <v>-0.561568702151706</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.745437820422728</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.270103587505876</v>
+        <v>-9.112966334051752</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5554324017887651</v>
+        <v>-0.4925775004071156</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.688266316260032</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.137828113874988</v>
+        <v>-8.980690860420864</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5071547255893831</v>
+        <v>-0.4442998242077336</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.555990842629146</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.947228439201835</v>
+        <v>-8.790091185747711</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4280997950324852</v>
+        <v>-0.3652448936508357</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.365391167955993</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.698228640518254</v>
+        <v>-8.54109138706413</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3155935343353939</v>
+        <v>-0.2527386329537444</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.365391167955993</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.803818630291358</v>
+        <v>-8.646681376837234</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4858054598438546</v>
+        <v>-0.4229505584622046</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.470981157729098</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.822553532409955</v>
+        <v>-8.665416278955831</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4447550788142069</v>
+        <v>-0.3819001774325574</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.470981157729098</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.674613491002356</v>
+        <v>-8.517476237548232</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5054579849393348</v>
+        <v>-0.4426030835576853</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.45066024182054</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.547721084567286</v>
+        <v>-8.390583831113162</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4634150086187847</v>
+        <v>-0.4005601072371352</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.32376783538547</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.504172677796594</v>
+        <v>-8.34703542434247</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4529562580056012</v>
+        <v>-0.3901013566239517</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.32376783538547</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.262024284342736</v>
+        <v>-8.104887030888612</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3416345462429149</v>
+        <v>-0.2787796448612654</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.32376783538547</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.82854791119281</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.198794912574389</v>
+        <v>-8.041657659120265</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3218106770763809</v>
+        <v>-0.2589557756947314</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.32376783538547</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.82804935326204</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.012307220197382</v>
+        <v>-7.855169966743259</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2497175061150014</v>
+        <v>-0.1868626047333524</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.137280143008464</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389902</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.991158021293939</v>
+        <v>-7.834020767839815</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2335568483162991</v>
+        <v>-0.1707019469346496</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.11613094410502</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.747392579310494</v>
+        <v>-7.590255325856371</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1402699631758706</v>
+        <v>-0.07741506179422109</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.11613094410502</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.82430765752752</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.483364512117234</v>
+        <v>-7.326227258663112</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03253442237855042</v>
+        <v>0.03032047900309864</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.914265545289067</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.233514118168159</v>
+        <v>-7.076376864714037</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06014781018478166</v>
+        <v>0.1230027115664307</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.914265545289067</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.92994662916418</v>
+        <v>-6.772809375710058</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1851739293070218</v>
+        <v>0.2480288306886709</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.914265545289067</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.856466720312167</v>
+        <v>-6.699329466858044</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2278933989023813</v>
+        <v>0.2907483002840299</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.840785636437053</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.631433720643344</v>
+        <v>-6.474296467189221</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3169270763862073</v>
+        <v>0.3797819777678564</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.61575263676823</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.416799343006937</v>
+        <v>-6.259662089552815</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4074756284950873</v>
+        <v>0.4703305298767364</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.401118259131823</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.259661189414186</v>
+        <v>-6.139924064981168</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4515251487159833</v>
+        <v>0.4994199984891905</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.401118259131823</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.019230692609326</v>
+        <v>-5.899493568176307</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5494404240628046</v>
+        <v>0.5973352738360123</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.160687762326963</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837678</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.77643988495988</v>
+        <v>-5.656702760526862</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.650486060957403</v>
+        <v>0.6983809107306107</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.160687762326963</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349961</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.53683479335279</v>
+        <v>-5.417097668919773</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7470066815175791</v>
+        <v>0.7949015312907863</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.093639814658468</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972334</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.294179204929627</v>
+        <v>-5.174442080496609</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8410669881068382</v>
+        <v>0.888961837880045</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.093639814658468</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.074158406892616</v>
+        <v>-4.954421282459599</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9306543443322566</v>
+        <v>0.9785491941054634</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.952419969590488</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.874909776987807</v>
+        <v>-4.75517265255479</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.026247979096004</v>
+        <v>1.07414282886921</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.952419969590488</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.715394673468437</v>
+        <v>-4.59565754903542</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.091199864944053</v>
+        <v>1.13909471471726</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7929048660711181</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.5707225283687</v>
+        <v>-4.450985403935682</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.159156825545388</v>
+        <v>1.207051675318595</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6482327209713807</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.552953069437744</v>
+        <v>-4.433215945004727</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.081604301204492</v>
+        <v>1.129499150977699</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6304632620404251</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.466153571658735</v>
+        <v>-4.346416447225717</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138724593638662</v>
+        <v>1.186619443411869</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6304632620404251</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.366460956929723</v>
+        <v>-4.246723832496706</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.178674040903679</v>
+        <v>1.226568890676886</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5307706473114133</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.434831143253733</v>
+        <v>-4.315094018820716</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.162332888848777</v>
+        <v>1.210227738621984</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5214949482751984</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.313414713627257</v>
+        <v>-4.193677589194239</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.201336169331259</v>
+        <v>1.249231019104466</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5214949482751984</v>
@@ -46119,22 +46119,45 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.409196486579662</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.001716924589848</v>
+        <v>-4.224670748522945</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.150724849986609</v>
+        <v>1.06154332041337</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5214949482751984</v>
       </c>
       <c r="G1938" t="n">
         <v>2.438871075171177</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="2" t="n">
+        <v>45401</v>
+      </c>
+      <c r="B1939" t="n">
+        <v>3.408205937754017</v>
+      </c>
+      <c r="C1939" t="n">
+        <v>2.559397838949542</v>
+      </c>
+      <c r="D1939" t="n">
+        <v>-4.224670748522945</v>
+      </c>
+      <c r="E1939" t="n">
+        <v>1.06154332041337</v>
+      </c>
+      <c r="F1939" t="n">
+        <v>-0.5214949482751984</v>
+      </c>
+      <c r="G1939" t="n">
+        <v>2.552461635935909</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240419.xlsx
+++ b/tame_output/ON/bt/strategyON_20240419.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-20.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.5%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.1%</t>
+          <t>136.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-708.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.0%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.7%</t>
+          <t>788.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-584.0%</t>
+          <t>-555.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-278.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-45.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.1%</t>
+          <t>-258.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-162.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-276.1%</t>
+          <t>-265.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,37 +1466,37 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-190.8%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.781621938432703</v>
+        <v>-5.643043212028227</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8044192612362524</v>
+        <v>0.8598507517980432</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.09421925808919</v>
+        <v>-0.9858311556919254</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.460892906069568</v>
+        <v>2.525925767507927</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.14674932107145</v>
+        <v>-6.008170594666974</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.657622823186585</v>
+        <v>0.7130543137483758</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.390530042388202</v>
+        <v>-1.282141939990938</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.282360950495991</v>
+        <v>2.34739381193435</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.555338098252129</v>
+        <v>-6.416759371847652</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4929488563290727</v>
+        <v>0.5483803468908635</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.799118819568881</v>
+        <v>-1.690730717171616</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.035969228202344</v>
+        <v>2.101002089640702</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.968320582393223</v>
+        <v>-6.829741855988746</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.322941295144096</v>
+        <v>0.3783727857058867</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.799118819568881</v>
+        <v>-1.690730717171616</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.031154660673804</v>
+        <v>2.096187522112163</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.38471245668022</v>
+        <v>-7.246133730275743</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1543785960381743</v>
+        <v>0.209810086599965</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.799118819568881</v>
+        <v>-1.690730717171616</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.029148711282682</v>
+        <v>2.09418157272104</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.761389467210065</v>
+        <v>-7.622810740805588</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0139664824949155</v>
+        <v>0.06939797305670625</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.799118819568881</v>
+        <v>-1.690730717171616</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.039407401951361</v>
+        <v>2.104440263389719</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.107264289194873</v>
+        <v>-7.968685562790396</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1282838811533127</v>
+        <v>-0.07285239059152193</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.799118819568881</v>
+        <v>-1.690730717171616</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.035506967097056</v>
+        <v>2.100539828535414</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.420089088439852</v>
+        <v>-8.281510362035375</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2550088807963031</v>
+        <v>-0.1995773902345124</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.799118819568881</v>
+        <v>-1.690730717171616</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.033911887152057</v>
+        <v>2.098944748590415</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.71675043025005</v>
+        <v>-8.578171703845573</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3698944415911742</v>
+        <v>-0.3144629510293835</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.759473852905495</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.996444981640938</v>
+        <v>2.061477843079296</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.150099538360285</v>
+        <v>-9.011520811955808</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5472603893696717</v>
+        <v>-0.4918288988078809</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.759473852905495</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.992418677106535</v>
+        <v>2.057451538544893</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.533100927102916</v>
+        <v>-9.394522200698439</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7005630461883081</v>
+        <v>-0.6451315556265174</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.867861955302759</v>
+        <v>-1.759473852905495</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.992316575784951</v>
+        <v>2.057349437223309</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.908086253274194</v>
+        <v>-9.769507526869717</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8479856606853891</v>
+        <v>-0.7925541701235983</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.242847281474037</v>
+        <v>-2.134459179076772</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.769896896053614</v>
+        <v>1.834929757491973</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.2676165757782</v>
+        <v>-10.12903784937372</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.986447486388939</v>
+        <v>-0.9310159958271482</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.242847281474037</v>
+        <v>-2.134459179076772</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.775247199351664</v>
+        <v>1.840280060790023</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.59401660444321</v>
+        <v>-10.45543787803873</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.109091477897767</v>
+        <v>-1.053659987335977</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.56924731013905</v>
+        <v>-2.460859207741785</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.587323202109834</v>
+        <v>1.652356063548193</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.81316557251741</v>
+        <v>-10.67458684611293</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.193709314505677</v>
+        <v>-1.138277823943886</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.788396278213247</v>
+        <v>-2.680008175815983</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.458875571887084</v>
+        <v>1.523908433325443</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.80947464756099</v>
+        <v>-10.67089592115652</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.192232944523113</v>
+        <v>-1.136801453961322</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.788396278213247</v>
+        <v>-2.680008175815983</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.458875571887084</v>
+        <v>1.523908433325443</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.01373282289086</v>
+        <v>-10.87515409648638</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.268423017536416</v>
+        <v>-1.212991526974625</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.916035222827236</v>
+        <v>-2.807647120429972</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.387805402237333</v>
+        <v>1.452838263675692</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.23177059452204</v>
+        <v>-11.09319186811756</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.351155571704451</v>
+        <v>-1.29572408114266</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.090805990923135</v>
+        <v>-2.982417888525871</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.28742549586423</v>
+        <v>1.352458357302589</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.15830076285459</v>
+        <v>-11.01972203645011</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.306395937544051</v>
+        <v>-1.25096444698226</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.017336159255687</v>
+        <v>-2.908948056858422</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.34687909635812</v>
+        <v>1.411911957796479</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.33342518024113</v>
+        <v>-11.19484645383665</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.361890483751151</v>
+        <v>-1.30645899318936</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.19246057664223</v>
+        <v>-3.084072474244966</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.256359666673711</v>
+        <v>1.32139252811207</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.56787727425562</v>
+        <v>-11.42929854785114</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.462890486258543</v>
+        <v>-1.407458995696752</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.19246057664223</v>
+        <v>-3.084072474244966</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.249140501772115</v>
+        <v>1.314173363210474</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.85568111879286</v>
+        <v>-11.71710239238838</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.584684214847414</v>
+        <v>-1.529252724285624</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.480264421179469</v>
+        <v>-3.371876318782204</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.069786004275796</v>
+        <v>1.134818865714155</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.08550556595668</v>
+        <v>-11.94692683955221</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.675498203874388</v>
+        <v>-1.620066713312597</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.642911958249629</v>
+        <v>-3.534523855852365</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9733132718722559</v>
+        <v>1.038346133310614</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.31753448569295</v>
+        <v>-12.17895575928847</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.765616043139778</v>
+        <v>-1.710184552577987</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.596536553040788</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9387993821883165</v>
+        <v>1.003832243626675</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.26551897172413</v>
+        <v>-12.12694024531966</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.740819501865852</v>
+        <v>-1.685388011304061</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.596536553040788</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9427897178747173</v>
+        <v>1.007822579313076</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.40719081344825</v>
+        <v>-12.26861208704378</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.798963465454242</v>
+        <v>-1.743531974892451</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.704924655438052</v>
+        <v>-3.596536553040788</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9413144909759756</v>
+        <v>1.006347352414334</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.50609755390753</v>
+        <v>-12.36751882750305</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.82347275147308</v>
+        <v>-1.768041260911289</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.803831395897328</v>
+        <v>-3.695443293500063</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8970238568652826</v>
+        <v>0.9620567183036415</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.30694544667043</v>
+        <v>-12.16836672026595</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.756863042224924</v>
+        <v>-1.701431551663133</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.638508869947514</v>
+        <v>-3.53012076755025</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9831662387884879</v>
+        <v>1.048199100226847</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.08110029395102</v>
+        <v>-11.94252156754654</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.65694590810095</v>
+        <v>-1.60151441753916</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.596582194360351</v>
+        <v>-3.488194091963086</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.017901317176995</v>
+        <v>1.082934178615353</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.79482548162832</v>
+        <v>-11.65624675522385</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.541296838615813</v>
+        <v>-1.485865348054023</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.596582194360351</v>
+        <v>-3.488194091963086</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.019040461733054</v>
+        <v>1.084073323171412</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.84772076967261</v>
+        <v>-11.70914204326813</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.559821179671419</v>
+        <v>-1.50438968910963</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.591626848271904</v>
+        <v>-3.48323874587464</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.024647443548229</v>
+        <v>1.089680304986588</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.56381203874386</v>
+        <v>-11.42523331233938</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.440523983061284</v>
+        <v>-1.385092492499494</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.591626848271904</v>
+        <v>-3.48323874587464</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.030381147786865</v>
+        <v>1.095414009225224</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.44839111460576</v>
+        <v>-11.30981238820129</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.40409287579991</v>
+        <v>-1.34866138523812</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.367817821736544</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.089896439875857</v>
+        <v>1.154929301314216</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702407</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.18455424740169</v>
+        <v>-11.04597552099722</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.30844161023119</v>
+        <v>-1.2530101196694</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.367817821736544</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.08001295856295</v>
+        <v>1.145045820001309</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906223</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9173124465333</v>
+        <v>-10.77873372012882</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.203379450383205</v>
+        <v>-1.147947959821415</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.476205924133809</v>
+        <v>-3.367817821736544</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.078178398063576</v>
+        <v>1.143211259501935</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.64150328313281</v>
+        <v>-10.50292455672834</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.093356099996472</v>
+        <v>-1.037924609434681</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.387186615855075</v>
+        <v>-3.278798513457811</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.131289668057355</v>
+        <v>1.196322529495714</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61754974215685</v>
+        <v>-10.47897101575238</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.083106177460595</v>
+        <v>-1.027674686898805</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.363233074879118</v>
+        <v>-3.254844972481853</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.146330298788424</v>
+        <v>1.211363160226782</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.35348980383406</v>
+        <v>-10.21491107742958</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9907425182932279</v>
+        <v>-0.935311027731438</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.099173136556322</v>
+        <v>-2.990785034159057</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.291505945620349</v>
+        <v>1.356538807058708</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.646410180329219</v>
+        <v>-9.507831453924744</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7106977025515944</v>
+        <v>-0.6552662119898041</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.099173136556322</v>
+        <v>-2.990785034159057</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.288718911960048</v>
+        <v>1.353751773398407</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.606225881963029</v>
+        <v>-9.467647155558554</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6942803593172768</v>
+        <v>-0.6388488687554865</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.058988838190131</v>
+        <v>-2.950600735792866</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.313173114867604</v>
+        <v>1.378205976305963</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.526156086425225</v>
+        <v>-9.387577360020749</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6628856198813979</v>
+        <v>-0.6074541293196081</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.978919042652327</v>
+        <v>-2.870530940255062</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.360581813411043</v>
+        <v>1.425614674849402</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.292674864195625</v>
+        <v>-9.15409613779115</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.561568702151706</v>
+        <v>-0.5061372115899156</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.745437820422728</v>
+        <v>-2.637049718025464</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.508594975586655</v>
+        <v>1.573627837025014</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.112966334051752</v>
+        <v>-8.974387607647277</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4925775004071156</v>
+        <v>-0.4371460098453257</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.688266316260032</v>
+        <v>-2.579878213862768</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.540005667771313</v>
+        <v>1.605038529209672</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.980690860420864</v>
+        <v>-8.842112134016389</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4442998242077336</v>
+        <v>-0.3888683336459438</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.555990842629146</v>
+        <v>-2.447602740231881</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.614738438696872</v>
+        <v>1.679771300135231</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.790091185747711</v>
+        <v>-8.651512459343236</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3652448936508357</v>
+        <v>-0.3098134030890454</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.365391167955993</v>
+        <v>-2.257003065558729</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.731913304188401</v>
+        <v>1.796946165626759</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.54109138706413</v>
+        <v>-8.402512660659655</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2527386329537444</v>
+        <v>-0.1973071423919541</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.365391167955993</v>
+        <v>-2.257003065558729</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.744819645412059</v>
+        <v>1.809852506850418</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.646681376837234</v>
+        <v>-8.508102650432759</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4229505584622046</v>
+        <v>-0.3675190679004148</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.470981157729098</v>
+        <v>-2.362593055331833</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.553489721948978</v>
+        <v>1.618522583387337</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.665416278955831</v>
+        <v>-8.526837552551356</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3819001774325574</v>
+        <v>-0.3264686868707671</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.470981157729098</v>
+        <v>-2.362593055331833</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.602034063826064</v>
+        <v>1.667066925264423</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.517476237548232</v>
+        <v>-8.378897511143757</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4426030835576853</v>
+        <v>-0.387171592995895</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.45066024182054</v>
+        <v>-2.342272139423276</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.494347690683031</v>
+        <v>1.55938055212139</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.390583831113162</v>
+        <v>-8.252005104708687</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4005601072371352</v>
+        <v>-0.3451286166753453</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.32376783538547</v>
+        <v>-2.215379732988206</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.561769148290595</v>
+        <v>1.626802009728954</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.34703542434247</v>
+        <v>-8.208456697937995</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3901013566239517</v>
+        <v>-0.3346698660621619</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.32376783538547</v>
+        <v>-2.215379732988206</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.554808536195502</v>
+        <v>1.619841397633861</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.104887030888612</v>
+        <v>-7.966308304484137</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2787796448612654</v>
+        <v>-0.2233481542994755</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.32376783538547</v>
+        <v>-2.215379732988206</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.569270890576645</v>
+        <v>1.634303752015004</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.041657659120265</v>
+        <v>-7.903078932715789</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2589557756947314</v>
+        <v>-0.2035242851329411</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.32376783538547</v>
+        <v>-2.215379732988206</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.56380301103584</v>
+        <v>1.628835872474199</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.855169966743259</v>
+        <v>-7.716591240338783</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1868626047333524</v>
+        <v>-0.1314311141715616</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.137280143008464</v>
+        <v>-2.028892040611199</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.673193720472621</v>
+        <v>1.738226581910979</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.834020767839815</v>
+        <v>-7.695442041435339</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1707019469346496</v>
+        <v>-0.1152704563728593</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.11613094410502</v>
+        <v>-2.007742841707756</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.693584218052012</v>
+        <v>1.758617079490371</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.590255325856371</v>
+        <v>-7.451676599451895</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07741506179422109</v>
+        <v>-0.02198357123243078</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.11613094410502</v>
+        <v>-2.007742841707756</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.689364926399063</v>
+        <v>1.754397787837421</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.326227258663112</v>
+        <v>-7.187648532258635</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.03032047900309864</v>
+        <v>0.0857519695648894</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.914265545289067</v>
+        <v>-1.805877442891802</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.812608479608651</v>
+        <v>1.877641341047009</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.076376864714037</v>
+        <v>-6.93779813830956</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1230027115664307</v>
+        <v>0.1784342021282215</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.914265545289067</v>
+        <v>-1.805877442891802</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.805350554592353</v>
+        <v>1.870383416030712</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.772809375710058</v>
+        <v>-6.634230649305581</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2480288306886709</v>
+        <v>0.3034603212504616</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.914265545289067</v>
+        <v>-1.805877442891802</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.808949678113002</v>
+        <v>1.87398253955136</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.699329466858044</v>
+        <v>-6.560750740453567</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2907483002840299</v>
+        <v>0.3461797908458206</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.840785636437053</v>
+        <v>-1.732397534039788</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.866365129478764</v>
+        <v>1.931397990917123</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.474296467189221</v>
+        <v>-6.335717740784744</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3797819777678564</v>
+        <v>0.4352134683296471</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.61575263676823</v>
+        <v>-1.507364534370965</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.000405406896355</v>
+        <v>2.065438268334713</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.259662089552815</v>
+        <v>-6.121083363148338</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4703305298767364</v>
+        <v>0.5257620204385272</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.401118259131823</v>
+        <v>-1.292730156734558</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.133880834532516</v>
+        <v>2.198913695970875</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.139924064981168</v>
+        <v>-5.854483006173986</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4994199984891905</v>
+        <v>0.6135964220120633</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.401118259131823</v>
+        <v>-1.292730156734558</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.115075093316312</v>
+        <v>2.18010795475467</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.899493568176307</v>
+        <v>-5.614052509369126</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5973352738360123</v>
+        <v>0.7115116973588851</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.160687762326963</v>
+        <v>-1.052299659929698</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.261076468024105</v>
+        <v>2.326109329462464</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.656702760526862</v>
+        <v>-5.37126170171968</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6983809107306107</v>
+        <v>0.8125573342534831</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.160687762326963</v>
+        <v>-1.052299659929698</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.265005781858926</v>
+        <v>2.330038643297284</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.417097668919773</v>
+        <v>-5.131656610112591</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7949015312907863</v>
+        <v>0.9090779548136587</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.093639814658468</v>
+        <v>-0.9852517122612036</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.305913134377362</v>
+        <v>2.370945995815721</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.174442080496609</v>
+        <v>-4.889001021689428</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.888961837880045</v>
+        <v>1.003138261402918</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.093639814658468</v>
+        <v>-0.9852517122612036</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.302911205597356</v>
+        <v>2.367944067035714</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.954421282459599</v>
+        <v>-4.668980223652417</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9785491941054634</v>
+        <v>1.092725617628336</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.952419969590488</v>
+        <v>-0.8440318671932233</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.389222149648758</v>
+        <v>2.454255011087116</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.75517265255479</v>
+        <v>-4.469731593747608</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.07414282886921</v>
+        <v>1.188319252392083</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.952419969590488</v>
+        <v>-0.8440318671932233</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.405116332450581</v>
+        <v>2.47014919388894</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.59565754903542</v>
+        <v>-4.310216490228238</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.13909471471726</v>
+        <v>1.253271138240133</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7929048660711181</v>
+        <v>-0.6845167636738534</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.501971239002505</v>
+        <v>2.567004100440863</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.450985403935682</v>
+        <v>-4.165544345128501</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.207051675318595</v>
+        <v>1.321228098841468</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6482327209713807</v>
+        <v>-0.5398446185741159</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.598862628623787</v>
+        <v>2.663895490062146</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.433215945004727</v>
+        <v>-4.147774886197545</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.129499150977699</v>
+        <v>1.243675574500572</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6304632620404251</v>
+        <v>-0.5220751596431603</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.524863996069082</v>
+        <v>2.589896857507441</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.346416447225717</v>
+        <v>-4.060975388418536</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.186619443411869</v>
+        <v>1.300795866934741</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6304632620404251</v>
+        <v>-0.5220751596431603</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.547264489391648</v>
+        <v>2.612297350830007</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.246723832496706</v>
+        <v>-3.961282773689524</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.226568890676886</v>
+        <v>1.340745314199758</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5307706473114133</v>
+        <v>-0.4223825449141486</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.607152459602467</v>
+        <v>2.672185321040826</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.315094018820716</v>
+        <v>-4.029652960013534</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.210227738621984</v>
+        <v>1.324404162144856</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5214949482751984</v>
+        <v>-0.4131068458779336</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.623724801498899</v>
+        <v>2.688757662937257</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.193677589194239</v>
+        <v>-3.908236530387057</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.249231019104466</v>
+        <v>1.363407442627338</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5214949482751984</v>
+        <v>-0.4131068458779336</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.61416151013079</v>
+        <v>2.679194371569149</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.224670748522945</v>
+        <v>-3.939229689715763</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.06154332041337</v>
+        <v>1.175719743936243</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5214949482751984</v>
+        <v>-0.4131068458779336</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.438871075171177</v>
+        <v>2.503903936609535</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.408205937754017</v>
+        <v>3.780319523642146</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.559397838949542</v>
+        <v>2.913059695391212</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.224670748522945</v>
+        <v>-3.939229689715763</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.06154332041337</v>
+        <v>1.175719743936243</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5214949482751984</v>
+        <v>-0.4131068458779336</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.552461635935909</v>
+        <v>2.90612349237758</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240419.xlsx
+++ b/tame_output/ON/bt/strategyON_20240419.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-46.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-708.6%</t>
+          <t>-709.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.7%</t>
+          <t>788.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-555.5%</t>
+          <t>-570.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.0%</t>
+          <t>-278.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-42.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-258.7%</t>
+          <t>-264.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.6%</t>
+          <t>-161.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-265.3%</t>
+          <t>-271.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-181.1%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.643043212028227</v>
+        <v>-5.781621938432703</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8598507517980432</v>
+        <v>0.8044192612362524</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9858311556919254</v>
+        <v>-1.09421925808919</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.525925767507927</v>
+        <v>2.460892906069568</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.008170594666974</v>
+        <v>-6.012070540868027</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7130543137483758</v>
+        <v>0.7114943352679544</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.282141939990938</v>
+        <v>-1.340075753309085</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.34739381193435</v>
+        <v>2.312633523943462</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.416759371847652</v>
+        <v>-6.420659318048706</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5483803468908635</v>
+        <v>0.546820368410442</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.690730717171616</v>
+        <v>-1.748664530489763</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.101002089640702</v>
+        <v>2.066241801649814</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.829741855988746</v>
+        <v>-6.8336418021898</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3783727857058867</v>
+        <v>0.3768128072254648</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.690730717171616</v>
+        <v>-1.748664530489763</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.096187522112163</v>
+        <v>2.061427234121274</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.246133730275743</v>
+        <v>-7.250033676476797</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.209810086599965</v>
+        <v>0.2082501081195431</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.690730717171616</v>
+        <v>-1.748664530489763</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.09418157272104</v>
+        <v>2.059421284730152</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.622810740805588</v>
+        <v>-7.626710687006642</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06939797305670625</v>
+        <v>0.06783799457628437</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.690730717171616</v>
+        <v>-1.748664530489763</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.104440263389719</v>
+        <v>2.069679975398831</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.968685562790396</v>
+        <v>-7.97258550899145</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.07285239059152193</v>
+        <v>-0.07441236907194382</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.690730717171616</v>
+        <v>-1.748664530489763</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.100539828535414</v>
+        <v>2.065779540544526</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.281510362035375</v>
+        <v>-8.285410308236429</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1995773902345124</v>
+        <v>-0.2011373687149343</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.690730717171616</v>
+        <v>-1.748664530489763</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.098944748590415</v>
+        <v>2.064184460599527</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.578171703845573</v>
+        <v>-8.582071650046627</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3144629510293835</v>
+        <v>-0.3160229295098054</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.759473852905495</v>
+        <v>-1.817407666223642</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.061477843079296</v>
+        <v>2.026717555088408</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.011520811955808</v>
+        <v>-9.015420758156862</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4918288988078809</v>
+        <v>-0.4933888772883024</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.759473852905495</v>
+        <v>-1.817407666223642</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.057451538544893</v>
+        <v>2.022691250554005</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.394522200698439</v>
+        <v>-9.398422146899494</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6451315556265174</v>
+        <v>-0.6466915341069388</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.759473852905495</v>
+        <v>-1.817407666223642</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.057349437223309</v>
+        <v>2.022589149232421</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.769507526869717</v>
+        <v>-9.773407473070771</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7925541701235983</v>
+        <v>-0.7941141486040197</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.134459179076772</v>
+        <v>-2.192392992394919</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.834929757491973</v>
+        <v>1.800169469501085</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.12903784937372</v>
+        <v>-10.13293779557477</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9310159958271482</v>
+        <v>-0.9325759743075706</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.134459179076772</v>
+        <v>-2.192392992394919</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.840280060790023</v>
+        <v>1.805519772799135</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.45543787803873</v>
+        <v>-10.45933782423979</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.053659987335977</v>
+        <v>-1.055219965816398</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.460859207741785</v>
+        <v>-2.518793021059933</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.652356063548193</v>
+        <v>1.617595775557304</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776675</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.67458684611293</v>
+        <v>-10.67848679231398</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.138277823943886</v>
+        <v>-1.139837802424308</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.680008175815983</v>
+        <v>-2.73794198913413</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.523908433325443</v>
+        <v>1.489148145334555</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67089592115652</v>
+        <v>-10.67479586735757</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.136801453961322</v>
+        <v>-1.138361432441744</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.680008175815983</v>
+        <v>-2.73794198913413</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.523908433325443</v>
+        <v>1.489148145334555</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.87515409648638</v>
+        <v>-10.87905404268744</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.212991526974625</v>
+        <v>-1.214551505455047</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.807647120429972</v>
+        <v>-2.865580933748119</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.452838263675692</v>
+        <v>1.418077975684804</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.09319186811756</v>
+        <v>-11.09709181431861</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.29572408114266</v>
+        <v>-1.297284059623081</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.982417888525871</v>
+        <v>-3.040351701844018</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.352458357302589</v>
+        <v>1.3176980693117</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.01972203645011</v>
+        <v>-11.02362198265116</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.25096444698226</v>
+        <v>-1.252524425462681</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.908948056858422</v>
+        <v>-2.966881870176569</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.411911957796479</v>
+        <v>1.377151669805591</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.19484645383665</v>
+        <v>-11.19874640003771</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.30645899318936</v>
+        <v>-1.308018971669782</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.084072474244966</v>
+        <v>-3.142006287563113</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.32139252811207</v>
+        <v>1.286632240121181</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.42929854785114</v>
+        <v>-11.4331984940522</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.407458995696752</v>
+        <v>-1.409018974177174</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.084072474244966</v>
+        <v>-3.142006287563113</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.314173363210474</v>
+        <v>1.279413075219585</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.71710239238838</v>
+        <v>-11.72100233858944</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.529252724285624</v>
+        <v>-1.530812702766045</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.371876318782204</v>
+        <v>-3.429810132100351</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.134818865714155</v>
+        <v>1.100058577723266</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.94692683955221</v>
+        <v>-11.95082678575326</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.620066713312597</v>
+        <v>-1.621626691793018</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.534523855852365</v>
+        <v>-3.592457669170512</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.038346133310614</v>
+        <v>1.003585845319726</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.17895575928847</v>
+        <v>-12.18285570548952</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.710184552577987</v>
+        <v>-1.711744531058409</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.596536553040788</v>
+        <v>-3.654470366358935</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.003832243626675</v>
+        <v>0.969071955635787</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.12694024531966</v>
+        <v>-12.13084019152071</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.685388011304061</v>
+        <v>-1.686947989784483</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.596536553040788</v>
+        <v>-3.654470366358935</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.007822579313076</v>
+        <v>0.9730622913221878</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.26861208704378</v>
+        <v>-12.27251203324483</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.743531974892451</v>
+        <v>-1.745091953372873</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.596536553040788</v>
+        <v>-3.654470366358935</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.006347352414334</v>
+        <v>0.9715870644234461</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.36751882750305</v>
+        <v>-12.37141877370411</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.768041260911289</v>
+        <v>-1.769601239391711</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.695443293500063</v>
+        <v>-3.75337710681821</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9620567183036415</v>
+        <v>0.9272964303127531</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.16836672026595</v>
+        <v>-12.17226666646701</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.701431551663133</v>
+        <v>-1.702991530143554</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.53012076755025</v>
+        <v>-3.588054580868397</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.048199100226847</v>
+        <v>1.013438812235958</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.94252156754654</v>
+        <v>-11.94642151374759</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.60151441753916</v>
+        <v>-1.603074396019581</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.488194091963086</v>
+        <v>-3.546127905281233</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.082934178615353</v>
+        <v>1.048173890624465</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.65624675522385</v>
+        <v>-11.6601467014249</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.485865348054023</v>
+        <v>-1.487425326534443</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.488194091963086</v>
+        <v>-3.546127905281233</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.084073323171412</v>
+        <v>1.049313035180524</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.70914204326813</v>
+        <v>-11.71304198946919</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.50438968910963</v>
+        <v>-1.505949667590051</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.48323874587464</v>
+        <v>-3.541172559192787</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.089680304986588</v>
+        <v>1.054920016995699</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.42523331233938</v>
+        <v>-11.42913325854044</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.385092492499494</v>
+        <v>-1.386652470979914</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.48323874587464</v>
+        <v>-3.541172559192787</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.095414009225224</v>
+        <v>1.060653721234336</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425323</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.30981238820129</v>
+        <v>-11.31371233440234</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.34866138523812</v>
+        <v>-1.350221363718541</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.367817821736544</v>
+        <v>-3.425751635054691</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.154929301314216</v>
+        <v>1.120169013323328</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.04597552099722</v>
+        <v>-11.04987546719827</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.2530101196694</v>
+        <v>-1.254570098149821</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.367817821736544</v>
+        <v>-3.425751635054691</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.145045820001309</v>
+        <v>1.11028553201042</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.77873372012882</v>
+        <v>-10.92654797813375</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.147947959821415</v>
+        <v>-1.207073663023388</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.367817821736544</v>
+        <v>-3.425751635054691</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.143211259501935</v>
+        <v>1.108450971511047</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.50292455672834</v>
+        <v>-10.65073881473327</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.037924609434681</v>
+        <v>-1.097050312636655</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.278798513457811</v>
+        <v>-3.336732326775958</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.196322529495714</v>
+        <v>1.161562241504826</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.47897101575238</v>
+        <v>-10.62678527375731</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.027674686898805</v>
+        <v>-1.086800390100778</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.254844972481853</v>
+        <v>-3.3127787858</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.211363160226782</v>
+        <v>1.176602872235894</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.21491107742958</v>
+        <v>-10.36272533543452</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.935311027731438</v>
+        <v>-0.9944367309334119</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.990785034159057</v>
+        <v>-3.048718847477204</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.356538807058708</v>
+        <v>1.32177851906782</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.507831453924744</v>
+        <v>-9.655645711929678</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6552662119898041</v>
+        <v>-0.7143919151917775</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.990785034159057</v>
+        <v>-3.048718847477204</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.353751773398407</v>
+        <v>1.318991485407519</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.467647155558554</v>
+        <v>-9.615461413563487</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6388488687554865</v>
+        <v>-0.6979745719574599</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.950600735792866</v>
+        <v>-3.008534549111014</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.378205976305963</v>
+        <v>1.343445688315074</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.387577360020749</v>
+        <v>-9.535391618025683</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6074541293196081</v>
+        <v>-0.666579832521581</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.870530940255062</v>
+        <v>-2.92846475357321</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.425614674849402</v>
+        <v>1.390854386858514</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.15409613779115</v>
+        <v>-9.301910395796085</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5061372115899156</v>
+        <v>-0.5652629147918899</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.637049718025464</v>
+        <v>-2.694983531343611</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.573627837025014</v>
+        <v>1.538867549034125</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.974387607647277</v>
+        <v>-9.122201865652212</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4371460098453257</v>
+        <v>-0.4962717130472996</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.579878213862768</v>
+        <v>-2.637812027180915</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.605038529209672</v>
+        <v>1.570278241218784</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.842112134016389</v>
+        <v>-8.989926392021324</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3888683336459438</v>
+        <v>-0.4479940368479176</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.447602740231881</v>
+        <v>-2.505536553550029</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.679771300135231</v>
+        <v>1.645011012144343</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.651512459343236</v>
+        <v>-8.799326717348171</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3098134030890454</v>
+        <v>-0.3689391062910197</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.257003065558729</v>
+        <v>-2.314936878876876</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.796946165626759</v>
+        <v>1.762185877635871</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.402512660659655</v>
+        <v>-8.55032691866459</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1973071423919541</v>
+        <v>-0.2564328455939284</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.257003065558729</v>
+        <v>-2.314936878876876</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.809852506850418</v>
+        <v>1.77509221885953</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.508102650432759</v>
+        <v>-8.655916908437694</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3675190679004148</v>
+        <v>-0.4266447711023886</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.362593055331833</v>
+        <v>-2.420526868649981</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.618522583387337</v>
+        <v>1.583762295396448</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.526837552551356</v>
+        <v>-8.674651810556291</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3264686868707671</v>
+        <v>-0.3855943900727414</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.362593055331833</v>
+        <v>-2.420526868649981</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.667066925264423</v>
+        <v>1.632306637273535</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.378897511143757</v>
+        <v>-8.526711769148692</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.387171592995895</v>
+        <v>-0.4462972961978693</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.342272139423276</v>
+        <v>-2.400205952741423</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.55938055212139</v>
+        <v>1.524620264130502</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.252005104708687</v>
+        <v>-8.399819362713622</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3451286166753453</v>
+        <v>-0.4042543198773192</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.215379732988206</v>
+        <v>-2.273313546306353</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.626802009728954</v>
+        <v>1.592041721738065</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.208456697937995</v>
+        <v>-8.35627095594293</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3346698660621619</v>
+        <v>-0.3937955692641357</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.215379732988206</v>
+        <v>-2.273313546306353</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.619841397633861</v>
+        <v>1.585081109642972</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.966308304484137</v>
+        <v>-8.114122562489072</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2233481542994755</v>
+        <v>-0.2824738575014494</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.215379732988206</v>
+        <v>-2.273313546306353</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.634303752015004</v>
+        <v>1.599543464024115</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.903078932715789</v>
+        <v>-8.050893190720725</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2035242851329411</v>
+        <v>-0.2626499883349154</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.215379732988206</v>
+        <v>-2.273313546306353</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.628835872474199</v>
+        <v>1.59407558448331</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.716591240338783</v>
+        <v>-7.864405498343719</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1314311141715616</v>
+        <v>-0.1905568173735364</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.028892040611199</v>
+        <v>-2.086825853929346</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.738226581910979</v>
+        <v>1.703466293920091</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.695442041435339</v>
+        <v>-7.843256299440275</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1152704563728593</v>
+        <v>-0.1743961595748336</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.007742841707756</v>
+        <v>-2.065676655025903</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.758617079490371</v>
+        <v>1.723856791499482</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.451676599451895</v>
+        <v>-7.599490857456831</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.02198357123243078</v>
+        <v>-0.08110927443440508</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.007742841707756</v>
+        <v>-2.065676655025903</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.754397787837421</v>
+        <v>1.719637499846533</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.187648532258635</v>
+        <v>-7.335462790263572</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.0857519695648894</v>
+        <v>0.02662626636291465</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.805877442891802</v>
+        <v>-1.86381125620995</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.877641341047009</v>
+        <v>1.842881053056121</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.93779813830956</v>
+        <v>-7.085612396314497</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1784342021282215</v>
+        <v>0.1193084989262467</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.805877442891802</v>
+        <v>-1.86381125620995</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.870383416030712</v>
+        <v>1.835623128039823</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.634230649305581</v>
+        <v>-6.782044907310518</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3034603212504616</v>
+        <v>0.2443346180484869</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.805877442891802</v>
+        <v>-1.86381125620995</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.87398253955136</v>
+        <v>1.839222251560472</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.560750740453567</v>
+        <v>-6.708564998458504</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3461797908458206</v>
+        <v>0.2870540876438459</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.732397534039788</v>
+        <v>-1.790331347357935</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.931397990917123</v>
+        <v>1.896637702926234</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.335717740784744</v>
+        <v>-6.483531998789681</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4352134683296471</v>
+        <v>0.3760877651276724</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.507364534370965</v>
+        <v>-1.565298347689112</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.065438268334713</v>
+        <v>2.030677980343825</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.121083363148338</v>
+        <v>-6.268897621153275</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5257620204385272</v>
+        <v>0.4666363172365524</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.292730156734558</v>
+        <v>-1.350663970052706</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.198913695970875</v>
+        <v>2.164153407979986</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.854483006173986</v>
+        <v>-6.002297264178923</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6135964220120633</v>
+        <v>0.5544707188100886</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.292730156734558</v>
+        <v>-1.350663970052706</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.18010795475467</v>
+        <v>2.145347666763782</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.614052509369126</v>
+        <v>-5.761866767374062</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7115116973588851</v>
+        <v>0.6523859941569103</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.052299659929698</v>
+        <v>-1.110233473247845</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.326109329462464</v>
+        <v>2.291349041471575</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.37126170171968</v>
+        <v>-5.519075959724617</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8125573342534831</v>
+        <v>0.7534316310515083</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.052299659929698</v>
+        <v>-1.110233473247845</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.330038643297284</v>
+        <v>2.295278355306396</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.131656610112591</v>
+        <v>-5.279470868117528</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9090779548136587</v>
+        <v>0.849952251611684</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9852517122612036</v>
+        <v>-1.043185525579351</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.370945995815721</v>
+        <v>2.336185707824832</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.889001021689428</v>
+        <v>-5.036815279694364</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.003138261402918</v>
+        <v>0.9440125582009431</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9852517122612036</v>
+        <v>-1.043185525579351</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.367944067035714</v>
+        <v>2.333183779044826</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.668980223652417</v>
+        <v>-4.816794481657354</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.092725617628336</v>
+        <v>1.033599914426361</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8440318671932233</v>
+        <v>-0.9019656805113707</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.454255011087116</v>
+        <v>2.419494723096228</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.469731593747608</v>
+        <v>-4.617545851752545</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.188319252392083</v>
+        <v>1.129193549190108</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8440318671932233</v>
+        <v>-0.9019656805113707</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.47014919388894</v>
+        <v>2.435388905898051</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.310216490228238</v>
+        <v>-4.458030748233175</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.253271138240133</v>
+        <v>1.194145435038158</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6845167636738534</v>
+        <v>-0.7424505769920008</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.567004100440863</v>
+        <v>2.532243812449975</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.165544345128501</v>
+        <v>-4.313358603133437</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.321228098841468</v>
+        <v>1.262102395639493</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5398446185741159</v>
+        <v>-0.5977784318922634</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.663895490062146</v>
+        <v>2.629135202071257</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.147774886197545</v>
+        <v>-4.295589144202482</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.243675574500572</v>
+        <v>1.184549871298597</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5220751596431603</v>
+        <v>-0.5800089729613078</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.589896857507441</v>
+        <v>2.555136569516553</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.060975388418536</v>
+        <v>-4.208789646423472</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.300795866934741</v>
+        <v>1.241670163732767</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5220751596431603</v>
+        <v>-0.5800089729613078</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.612297350830007</v>
+        <v>2.577537062839119</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.961282773689524</v>
+        <v>-4.109097031694461</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.340745314199758</v>
+        <v>1.281619610997784</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4223825449141486</v>
+        <v>-0.4803163582322961</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.672185321040826</v>
+        <v>2.637425033049938</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.029652960013534</v>
+        <v>-4.177467218018471</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.324404162144856</v>
+        <v>1.265278458942882</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4131068458779336</v>
+        <v>-0.4710406591960811</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.688757662937257</v>
+        <v>2.653997374946369</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.908236530387057</v>
+        <v>-4.056050788391994</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.363407442627338</v>
+        <v>1.304281739425363</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4131068458779336</v>
+        <v>-0.4710406591960811</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.679194371569149</v>
+        <v>2.64443408357826</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.939229689715763</v>
+        <v>-4.0870439477207</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.175719743936243</v>
+        <v>1.116594040734268</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4131068458779336</v>
+        <v>-0.4710406591960811</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.503903936609535</v>
+        <v>2.469143648618647</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.780319523642146</v>
+        <v>3.819386522600148</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.913059695391212</v>
+        <v>2.656524815104623</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.939229689715763</v>
+        <v>-4.0870439477207</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.175719743936243</v>
+        <v>1.116594040734268</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4131068458779336</v>
+        <v>-0.4710406591960811</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.90612349237758</v>
+        <v>2.64958861209099</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240419.xlsx
+++ b/tame_output/ON/bt/strategyON_20240419.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-46.0%</t>
+          <t>-36.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>117.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.9%</t>
+          <t>138.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-709.0%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-58.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.5%</t>
+          <t>781.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.3%</t>
+          <t>-567.6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.2%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.0%</t>
+          <t>-45.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.6%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-264.6%</t>
+          <t>-263.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.9%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-271.1%</t>
+          <t>-289.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.1%</t>
+          <t>-209.9%</t>
         </is>
       </c>
     </row>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.012070540868027</v>
+        <v>-6.14674932107145</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7114943352679544</v>
+        <v>0.657622823186585</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.340075753309085</v>
+        <v>-1.390530042388202</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.312633523943462</v>
+        <v>2.282360950495991</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.420659318048706</v>
+        <v>-6.555338098252129</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.546820368410442</v>
+        <v>0.4929488563290727</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.748664530489763</v>
+        <v>-1.799118819568881</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.066241801649814</v>
+        <v>2.035969228202344</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.8336418021898</v>
+        <v>-6.968320582393223</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3768128072254648</v>
+        <v>0.322941295144096</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.748664530489763</v>
+        <v>-1.799118819568881</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.061427234121274</v>
+        <v>2.031154660673804</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.250033676476797</v>
+        <v>-7.38471245668022</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2082501081195431</v>
+        <v>0.1543785960381743</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.748664530489763</v>
+        <v>-1.799118819568881</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.059421284730152</v>
+        <v>2.029148711282682</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.626710687006642</v>
+        <v>-7.761389467210065</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06783799457628437</v>
+        <v>0.0139664824949155</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.748664530489763</v>
+        <v>-1.799118819568881</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.069679975398831</v>
+        <v>2.039407401951361</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.97258550899145</v>
+        <v>-8.107264289194873</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.07441236907194382</v>
+        <v>-0.1282838811533127</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.748664530489763</v>
+        <v>-1.799118819568881</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.065779540544526</v>
+        <v>2.035506967097056</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.285410308236429</v>
+        <v>-8.420089088439852</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2011373687149343</v>
+        <v>-0.2550088807963031</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.748664530489763</v>
+        <v>-1.799118819568881</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.064184460599527</v>
+        <v>2.033911887152057</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.582071650046627</v>
+        <v>-8.71675043025005</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3160229295098054</v>
+        <v>-0.3698944415911742</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.817407666223642</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.026717555088408</v>
+        <v>1.996444981640938</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.015420758156862</v>
+        <v>-9.150099538360285</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4933888772883024</v>
+        <v>-0.5472603893696717</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.817407666223642</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.022691250554005</v>
+        <v>1.992418677106535</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.398422146899494</v>
+        <v>-9.533100927102916</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6466915341069388</v>
+        <v>-0.7005630461883081</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.817407666223642</v>
+        <v>-1.867861955302759</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.022589149232421</v>
+        <v>1.992316575784951</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.773407473070771</v>
+        <v>-9.908086253274194</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7941141486040197</v>
+        <v>-0.8479856606853891</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.192392992394919</v>
+        <v>-2.242847281474037</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.800169469501085</v>
+        <v>1.769896896053614</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13293779557477</v>
+        <v>-10.2676165757782</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9325759743075706</v>
+        <v>-0.986447486388939</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.192392992394919</v>
+        <v>-2.242847281474037</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.805519772799135</v>
+        <v>1.775247199351664</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.45933782423979</v>
+        <v>-10.59401660444321</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.055219965816398</v>
+        <v>-1.109091477897767</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.518793021059933</v>
+        <v>-2.56924731013905</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.617595775557304</v>
+        <v>1.587323202109834</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.67848679231398</v>
+        <v>-10.81316557251741</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.139837802424308</v>
+        <v>-1.193709314505677</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.73794198913413</v>
+        <v>-2.788396278213247</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.489148145334555</v>
+        <v>1.458875571887084</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67479586735757</v>
+        <v>-10.80947464756099</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.138361432441744</v>
+        <v>-1.192232944523113</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.73794198913413</v>
+        <v>-2.788396278213247</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.489148145334555</v>
+        <v>1.458875571887084</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.87905404268744</v>
+        <v>-11.01373282289086</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.214551505455047</v>
+        <v>-1.268423017536416</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.865580933748119</v>
+        <v>-2.916035222827236</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.418077975684804</v>
+        <v>1.387805402237333</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.09709181431861</v>
+        <v>-11.23177059452204</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.297284059623081</v>
+        <v>-1.351155571704451</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.040351701844018</v>
+        <v>-3.090805990923135</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.3176980693117</v>
+        <v>1.28742549586423</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02362198265116</v>
+        <v>-11.15830076285459</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.252524425462681</v>
+        <v>-1.306395937544051</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.966881870176569</v>
+        <v>-3.017336159255687</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.377151669805591</v>
+        <v>1.34687909635812</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.19874640003771</v>
+        <v>-11.33342518024113</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.308018971669782</v>
+        <v>-1.361890483751151</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.142006287563113</v>
+        <v>-3.19246057664223</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.286632240121181</v>
+        <v>1.256359666673711</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4331984940522</v>
+        <v>-11.56787727425562</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.409018974177174</v>
+        <v>-1.462890486258543</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.142006287563113</v>
+        <v>-3.19246057664223</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.279413075219585</v>
+        <v>1.249140501772115</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72100233858944</v>
+        <v>-11.85568111879286</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.530812702766045</v>
+        <v>-1.584684214847414</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.429810132100351</v>
+        <v>-3.480264421179469</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.100058577723266</v>
+        <v>1.069786004275796</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95082678575326</v>
+        <v>-12.08550556595668</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.621626691793018</v>
+        <v>-1.675498203874388</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.592457669170512</v>
+        <v>-3.642911958249629</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.003585845319726</v>
+        <v>0.9733132718722559</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18285570548952</v>
+        <v>-12.31753448569295</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.711744531058409</v>
+        <v>-1.765616043139778</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.654470366358935</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.969071955635787</v>
+        <v>0.9387993821883165</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13084019152071</v>
+        <v>-12.26551897172413</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.686947989784483</v>
+        <v>-1.740819501865852</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.654470366358935</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9730622913221878</v>
+        <v>0.9427897178747173</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27251203324483</v>
+        <v>-12.40719081344825</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.745091953372873</v>
+        <v>-1.798963465454242</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.654470366358935</v>
+        <v>-3.704924655438052</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9715870644234461</v>
+        <v>0.9413144909759756</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.37141877370411</v>
+        <v>-12.50609755390753</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.769601239391711</v>
+        <v>-1.82347275147308</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.75337710681821</v>
+        <v>-3.803831395897328</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9272964303127531</v>
+        <v>0.8970238568652826</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.17226666646701</v>
+        <v>-12.30694544667043</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.702991530143554</v>
+        <v>-1.756863042224924</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.588054580868397</v>
+        <v>-3.638508869947514</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.013438812235958</v>
+        <v>0.9831662387884879</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.94642151374759</v>
+        <v>-12.08110029395102</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.603074396019581</v>
+        <v>-1.65694590810095</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.546127905281233</v>
+        <v>-3.596582194360351</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.048173890624465</v>
+        <v>1.017901317176995</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6601467014249</v>
+        <v>-11.79482548162832</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.487425326534443</v>
+        <v>-1.541296838615813</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.546127905281233</v>
+        <v>-3.596582194360351</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.049313035180524</v>
+        <v>1.019040461733054</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.71304198946919</v>
+        <v>-11.84772076967261</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.505949667590051</v>
+        <v>-1.559821179671419</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.541172559192787</v>
+        <v>-3.591626848271904</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.054920016995699</v>
+        <v>1.024647443548229</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.42913325854044</v>
+        <v>-11.56381203874386</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.386652470979914</v>
+        <v>-1.440523983061284</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.541172559192787</v>
+        <v>-3.591626848271904</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.060653721234336</v>
+        <v>1.030381147786865</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.31371233440234</v>
+        <v>-11.44839111460576</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.350221363718541</v>
+        <v>-1.40409287579991</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.425751635054691</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.120169013323328</v>
+        <v>1.089896439875857</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.04987546719827</v>
+        <v>-11.18455424740169</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.254570098149821</v>
+        <v>-1.30844161023119</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.425751635054691</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.11028553201042</v>
+        <v>1.08001295856295</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.92654797813375</v>
+        <v>-10.9173124465333</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.207073663023388</v>
+        <v>-1.203379450383205</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.425751635054691</v>
+        <v>-3.476205924133809</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.108450971511047</v>
+        <v>1.078178398063576</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.65073881473327</v>
+        <v>-10.64150328313281</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.097050312636655</v>
+        <v>-1.093356099996472</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.336732326775958</v>
+        <v>-3.387186615855075</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.161562241504826</v>
+        <v>1.131289668057355</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.62678527375731</v>
+        <v>-10.61754974215685</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.086800390100778</v>
+        <v>-1.083106177460595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.3127787858</v>
+        <v>-3.363233074879118</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.176602872235894</v>
+        <v>1.146330298788424</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.36272533543452</v>
+        <v>-10.35348980383406</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9944367309334119</v>
+        <v>-0.9907425182932279</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.048718847477204</v>
+        <v>-3.099173136556322</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.32177851906782</v>
+        <v>1.291505945620349</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.655645711929678</v>
+        <v>-9.646410180329219</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7143919151917775</v>
+        <v>-0.7106977025515944</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.048718847477204</v>
+        <v>-3.099173136556322</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.318991485407519</v>
+        <v>1.288718911960048</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.615461413563487</v>
+        <v>-9.606225881963029</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6979745719574599</v>
+        <v>-0.6942803593172768</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.008534549111014</v>
+        <v>-3.058988838190131</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.343445688315074</v>
+        <v>1.313173114867604</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.535391618025683</v>
+        <v>-9.526156086425225</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.666579832521581</v>
+        <v>-0.6628856198813979</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.92846475357321</v>
+        <v>-2.978919042652327</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.390854386858514</v>
+        <v>1.360581813411043</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.301910395796085</v>
+        <v>-9.292674864195625</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5652629147918899</v>
+        <v>-0.561568702151706</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.694983531343611</v>
+        <v>-2.745437820422728</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.538867549034125</v>
+        <v>1.508594975586655</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.122201865652212</v>
+        <v>-9.112966334051752</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4962717130472996</v>
+        <v>-0.4925775004071156</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.637812027180915</v>
+        <v>-2.688266316260032</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.570278241218784</v>
+        <v>1.540005667771313</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.989926392021324</v>
+        <v>-8.980690860420864</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4479940368479176</v>
+        <v>-0.4442998242077336</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.505536553550029</v>
+        <v>-2.555990842629146</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.645011012144343</v>
+        <v>1.614738438696872</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.799326717348171</v>
+        <v>-8.790091185747711</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3689391062910197</v>
+        <v>-0.3652448936508357</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.314936878876876</v>
+        <v>-2.365391167955993</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.762185877635871</v>
+        <v>1.731913304188401</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.55032691866459</v>
+        <v>-8.54109138706413</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2564328455939284</v>
+        <v>-0.2527386329537444</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.314936878876876</v>
+        <v>-2.365391167955993</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.77509221885953</v>
+        <v>1.744819645412059</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.655916908437694</v>
+        <v>-8.646681376837234</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4266447711023886</v>
+        <v>-0.4229505584622046</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.420526868649981</v>
+        <v>-2.470981157729098</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.583762295396448</v>
+        <v>1.553489721948978</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.674651810556291</v>
+        <v>-8.665416278955831</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3855943900727414</v>
+        <v>-0.3819001774325574</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.420526868649981</v>
+        <v>-2.470981157729098</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.632306637273535</v>
+        <v>1.602034063826064</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.526711769148692</v>
+        <v>-8.517476237548232</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4462972961978693</v>
+        <v>-0.4426030835576853</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.400205952741423</v>
+        <v>-2.45066024182054</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.524620264130502</v>
+        <v>1.494347690683031</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.399819362713622</v>
+        <v>-8.390583831113162</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4042543198773192</v>
+        <v>-0.4005601072371352</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.273313546306353</v>
+        <v>-2.32376783538547</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.592041721738065</v>
+        <v>1.561769148290595</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.35627095594293</v>
+        <v>-8.34703542434247</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3937955692641357</v>
+        <v>-0.3901013566239517</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.273313546306353</v>
+        <v>-2.32376783538547</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.585081109642972</v>
+        <v>1.554808536195502</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.114122562489072</v>
+        <v>-8.104887030888612</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2824738575014494</v>
+        <v>-0.2787796448612654</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.273313546306353</v>
+        <v>-2.32376783538547</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.599543464024115</v>
+        <v>1.569270890576645</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.050893190720725</v>
+        <v>-8.041657659120265</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2626499883349154</v>
+        <v>-0.2589557756947314</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.273313546306353</v>
+        <v>-2.32376783538547</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.59407558448331</v>
+        <v>1.56380301103584</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.864405498343719</v>
+        <v>-7.855169966743259</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1905568173735364</v>
+        <v>-0.1868626047333524</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.086825853929346</v>
+        <v>-2.137280143008464</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.703466293920091</v>
+        <v>1.673193720472621</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.843256299440275</v>
+        <v>-7.834020767839815</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1743961595748336</v>
+        <v>-0.1707019469346496</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.065676655025903</v>
+        <v>-2.11613094410502</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.723856791499482</v>
+        <v>1.693584218052012</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.599490857456831</v>
+        <v>-7.590255325856371</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.08110927443440508</v>
+        <v>-0.07741506179422109</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.065676655025903</v>
+        <v>-2.11613094410502</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.719637499846533</v>
+        <v>1.689364926399063</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.335462790263572</v>
+        <v>-7.326227258663112</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.02662626636291465</v>
+        <v>0.03032047900309864</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.86381125620995</v>
+        <v>-1.914265545289067</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.842881053056121</v>
+        <v>1.812608479608651</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.085612396314497</v>
+        <v>-7.076376864714037</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1193084989262467</v>
+        <v>0.1230027115664307</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.86381125620995</v>
+        <v>-1.914265545289067</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.835623128039823</v>
+        <v>1.805350554592353</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.782044907310518</v>
+        <v>-6.772809375710058</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2443346180484869</v>
+        <v>0.2480288306886709</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.86381125620995</v>
+        <v>-1.914265545289067</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.839222251560472</v>
+        <v>1.808949678113002</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.708564998458504</v>
+        <v>-6.699329466858044</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2870540876438459</v>
+        <v>0.2907483002840299</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.790331347357935</v>
+        <v>-1.840785636437053</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.896637702926234</v>
+        <v>1.866365129478764</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.483531998789681</v>
+        <v>-6.474296467189221</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3760877651276724</v>
+        <v>0.3797819777678564</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.565298347689112</v>
+        <v>-1.61575263676823</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.030677980343825</v>
+        <v>2.000405406896355</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.268897621153275</v>
+        <v>-6.259662089552815</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4666363172365524</v>
+        <v>0.4703305298767364</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.350663970052706</v>
+        <v>-1.401118259131823</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.164153407979986</v>
+        <v>2.133880834532516</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.002297264178923</v>
+        <v>-5.993061732578463</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5544707188100886</v>
+        <v>0.5581649314502726</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.350663970052706</v>
+        <v>-1.401118259131823</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.145347666763782</v>
+        <v>2.115075093316312</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.761866767374062</v>
+        <v>-5.889943734302254</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6523859941569103</v>
+        <v>0.6011552073856334</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.110233473247845</v>
+        <v>-1.298000260855614</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.291349041471575</v>
+        <v>2.178688968906914</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.519075959724617</v>
+        <v>-5.647152926652809</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7534316310515083</v>
+        <v>0.7022008442802319</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.110233473247845</v>
+        <v>-1.298000260855614</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.295278355306396</v>
+        <v>2.182618282741734</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.279470868117528</v>
+        <v>-5.407547835045719</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.849952251611684</v>
+        <v>0.798721464840408</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.043185525579351</v>
+        <v>-1.23095231318712</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.336185707824832</v>
+        <v>2.223525635260171</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.036815279694364</v>
+        <v>-5.164892246622555</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9440125582009431</v>
+        <v>0.8927817714296666</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.043185525579351</v>
+        <v>-1.23095231318712</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.333183779044826</v>
+        <v>2.220523706480164</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.816794481657354</v>
+        <v>-4.944871448585545</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.033599914426361</v>
+        <v>0.982369127655085</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9019656805113707</v>
+        <v>-1.08973246811914</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.419494723096228</v>
+        <v>2.306834650531567</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.617545851752545</v>
+        <v>-4.745622818680736</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.129193549190108</v>
+        <v>1.077962762418832</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9019656805113707</v>
+        <v>-1.08973246811914</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.435388905898051</v>
+        <v>2.32272883333339</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.458030748233175</v>
+        <v>-4.586107715161366</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.194145435038158</v>
+        <v>1.142914648266882</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7424505769920008</v>
+        <v>-0.9302173645997699</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.532243812449975</v>
+        <v>2.419583739885314</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.313358603133437</v>
+        <v>-4.441435570061628</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.262102395639493</v>
+        <v>1.210871608868217</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5977784318922634</v>
+        <v>-0.7855452195000325</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.629135202071257</v>
+        <v>2.516475129506596</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.295589144202482</v>
+        <v>-4.423666111130673</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.184549871298597</v>
+        <v>1.133319084527321</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5800089729613078</v>
+        <v>-0.7677757605690769</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.555136569516553</v>
+        <v>2.442476496951891</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.208789646423472</v>
+        <v>-4.336866613351663</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.241670163732767</v>
+        <v>1.19043937696149</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5800089729613078</v>
+        <v>-0.7677757605690769</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.577537062839119</v>
+        <v>2.464876990274457</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.109097031694461</v>
+        <v>-4.237173998622652</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.281619610997784</v>
+        <v>1.230388824226507</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4803163582322961</v>
+        <v>-0.6680831458400651</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.637425033049938</v>
+        <v>2.524764960485276</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.177467218018471</v>
+        <v>-4.305544184946662</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.265278458942882</v>
+        <v>1.214047672171605</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4710406591960811</v>
+        <v>-0.6588074468038502</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.653997374946369</v>
+        <v>2.541337302381707</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.056050788391994</v>
+        <v>-4.184127755320185</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.304281739425363</v>
+        <v>1.253050952654087</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4710406591960811</v>
+        <v>-0.6588074468038502</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.64443408357826</v>
+        <v>2.531774011013598</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.0870439477207</v>
+        <v>-4.215120914648891</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.116594040734268</v>
+        <v>1.065363253962992</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4710406591960811</v>
+        <v>-0.6588074468038502</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.469143648618647</v>
+        <v>2.356483576053985</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.819386522600148</v>
+        <v>3.407043036771678</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.656524815104623</v>
+        <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.0870439477207</v>
+        <v>-4.060474180603867</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.116594040734268</v>
+        <v>1.131789179572789</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4710406591960811</v>
+        <v>-0.6588074468038502</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.64958861209099</v>
+        <v>2.361050808045773</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240419.xlsx
+++ b/tame_output/ON/bt/strategyON_20240419.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-54.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>117.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>781.0%</t>
+          <t>780.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-567.6%</t>
+          <t>-581.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-263.0%</t>
+          <t>-287.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-289.9%</t>
+          <t>-290.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-209.9%</t>
+          <t>-228.9%</t>
         </is>
       </c>
     </row>
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.64150328313281</v>
+        <v>-10.80362409771839</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.093356099996472</v>
+        <v>-1.158204425830702</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.387186615855075</v>
+        <v>-3.389895483227113</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.131289668057355</v>
+        <v>1.129664347634133</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61754974215685</v>
+        <v>-10.77967055674243</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.083106177460595</v>
+        <v>-1.147954503294826</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.363233074879118</v>
+        <v>-3.365941942251156</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.146330298788424</v>
+        <v>1.144704978365201</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.35348980383406</v>
+        <v>-10.51561061841963</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9907425182932279</v>
+        <v>-1.055590844127459</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.099173136556322</v>
+        <v>-3.101882003928359</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.291505945620349</v>
+        <v>1.289880625197127</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.646410180329219</v>
+        <v>-9.808530994914797</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7106977025515944</v>
+        <v>-0.7755460283858251</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.099173136556322</v>
+        <v>-3.101882003928359</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.288718911960048</v>
+        <v>1.287093591536826</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.606225881963029</v>
+        <v>-9.768346696548607</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6942803593172768</v>
+        <v>-0.7591286851515076</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.058988838190131</v>
+        <v>-3.061697705562168</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.313173114867604</v>
+        <v>1.311547794444382</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.526156086425225</v>
+        <v>-9.688276901010802</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6628856198813979</v>
+        <v>-0.7277339457156291</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.978919042652327</v>
+        <v>-2.981627910024364</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.360581813411043</v>
+        <v>1.358956492987821</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.292674864195625</v>
+        <v>-9.454795678781203</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.561568702151706</v>
+        <v>-0.6264170279859367</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.745437820422728</v>
+        <v>-2.748146687794766</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.508594975586655</v>
+        <v>1.506969655163432</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.112966334051752</v>
+        <v>-9.275087148637329</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4925775004071156</v>
+        <v>-0.5574258262413467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.688266316260032</v>
+        <v>-2.69097518363207</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.540005667771313</v>
+        <v>1.538380347348091</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.980690860420864</v>
+        <v>-9.142811675006442</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4442998242077336</v>
+        <v>-0.5091481500419648</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.555990842629146</v>
+        <v>-2.558699710001183</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.614738438696872</v>
+        <v>1.61311311827365</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.790091185747711</v>
+        <v>-8.952212000333288</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3652448936508357</v>
+        <v>-0.4300932194850664</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.365391167955993</v>
+        <v>-2.368100035328031</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.731913304188401</v>
+        <v>1.730287983765178</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.54109138706413</v>
+        <v>-8.703212201649707</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2527386329537444</v>
+        <v>-0.3175869587879752</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.365391167955993</v>
+        <v>-2.368100035328031</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.744819645412059</v>
+        <v>1.743194324988837</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.646681376837234</v>
+        <v>-8.808802191422812</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4229505584622046</v>
+        <v>-0.4877988842964358</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.470981157729098</v>
+        <v>-2.473690025101135</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.553489721948978</v>
+        <v>1.551864401525755</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.665416278955831</v>
+        <v>-8.827537093541409</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3819001774325574</v>
+        <v>-0.4467485032667882</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.470981157729098</v>
+        <v>-2.473690025101135</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.602034063826064</v>
+        <v>1.600408743402842</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.517476237548232</v>
+        <v>-8.679597052133809</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4426030835576853</v>
+        <v>-0.507451409391916</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.45066024182054</v>
+        <v>-2.453369109192578</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.494347690683031</v>
+        <v>1.492722370259809</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.390583831113162</v>
+        <v>-8.552704645698739</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4005601072371352</v>
+        <v>-0.4654084330713664</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.32376783538547</v>
+        <v>-2.326476702757508</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.561769148290595</v>
+        <v>1.560143827867372</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.34703542434247</v>
+        <v>-8.509156238928048</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3901013566239517</v>
+        <v>-0.4549496824581829</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.32376783538547</v>
+        <v>-2.326476702757508</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.554808536195502</v>
+        <v>1.553183215772279</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.104887030888612</v>
+        <v>-8.26700784547419</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2787796448612654</v>
+        <v>-0.3436279706954966</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.32376783538547</v>
+        <v>-2.326476702757508</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.569270890576645</v>
+        <v>1.567645570153422</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.041657659120265</v>
+        <v>-8.203778473705842</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2589557756947314</v>
+        <v>-0.3238041015289626</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.32376783538547</v>
+        <v>-2.326476702757508</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.56380301103584</v>
+        <v>1.562177690612617</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.855169966743259</v>
+        <v>-8.017290781328835</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1868626047333524</v>
+        <v>-0.2517109305675826</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.137280143008464</v>
+        <v>-2.139989010380501</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.673193720472621</v>
+        <v>1.671568400049398</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.834020767839815</v>
+        <v>-7.996141582425392</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1707019469346496</v>
+        <v>-0.2355502727688803</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.11613094410502</v>
+        <v>-2.118839811477058</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.693584218052012</v>
+        <v>1.691958897628789</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.590255325856371</v>
+        <v>-7.752376140441948</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07741506179422109</v>
+        <v>-0.1422633876284518</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.11613094410502</v>
+        <v>-2.118839811477058</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.689364926399063</v>
+        <v>1.68773960597584</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.326227258663112</v>
+        <v>-7.488348073248687</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.03032047900309864</v>
+        <v>-0.03452784683113164</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.914265545289067</v>
+        <v>-1.916974412661104</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.812608479608651</v>
+        <v>1.810983159185428</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.076376864714037</v>
+        <v>-7.238497679299613</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1230027115664307</v>
+        <v>0.05815438573220044</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.914265545289067</v>
+        <v>-1.916974412661104</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.805350554592353</v>
+        <v>1.80372523416913</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.772809375710058</v>
+        <v>-6.934930190295634</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2480288306886709</v>
+        <v>0.1831805048544406</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.914265545289067</v>
+        <v>-1.916974412661104</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.808949678113002</v>
+        <v>1.807324357689779</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.699329466858044</v>
+        <v>-6.86145028144362</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2907483002840299</v>
+        <v>0.2258999744497996</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.840785636437053</v>
+        <v>-1.84349450380909</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.866365129478764</v>
+        <v>1.864739809055541</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.474296467189221</v>
+        <v>-6.636417281774797</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3797819777678564</v>
+        <v>0.3149336519336261</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.61575263676823</v>
+        <v>-1.618461504140267</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.000405406896355</v>
+        <v>1.998780086473132</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.259662089552815</v>
+        <v>-6.42178290413839</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4703305298767364</v>
+        <v>0.4054822040425061</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.401118259131823</v>
+        <v>-1.40382712650386</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.133880834532516</v>
+        <v>2.132255514109294</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.993061732578463</v>
+        <v>-6.155182547164038</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5581649314502726</v>
+        <v>0.4933166056160423</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.401118259131823</v>
+        <v>-1.40382712650386</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.115075093316312</v>
+        <v>2.113449772893089</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.889943734302254</v>
+        <v>-6.05206454888783</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6011552073856334</v>
+        <v>0.5363068815514032</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.298000260855614</v>
+        <v>-1.300709128227652</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.178688968906914</v>
+        <v>2.177063648483692</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.647152926652809</v>
+        <v>-5.809273741238385</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7022008442802319</v>
+        <v>0.6373525184460016</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.298000260855614</v>
+        <v>-1.300709128227652</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.182618282741734</v>
+        <v>2.180992962318512</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.407547835045719</v>
+        <v>-5.569668649631295</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.798721464840408</v>
+        <v>0.7338731390061777</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.23095231318712</v>
+        <v>-1.233661180559158</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.223525635260171</v>
+        <v>2.221900314836948</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.164892246622555</v>
+        <v>-5.327013061208131</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8927817714296666</v>
+        <v>0.8279334455954364</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.23095231318712</v>
+        <v>-1.233661180559158</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.220523706480164</v>
+        <v>2.218898386056942</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.944871448585545</v>
+        <v>-5.10699226317112</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.982369127655085</v>
+        <v>0.9175208018208547</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.08973246811914</v>
+        <v>-1.092441335491177</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.306834650531567</v>
+        <v>2.305209330108344</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.745622818680736</v>
+        <v>-4.907743633266311</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.077962762418832</v>
+        <v>1.013114436584602</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.08973246811914</v>
+        <v>-1.092441335491177</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.32272883333339</v>
+        <v>2.321103512910168</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.586107715161366</v>
+        <v>-4.748228529746942</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.142914648266882</v>
+        <v>1.078066322432651</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9302173645997699</v>
+        <v>-0.9329262319718074</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.419583739885314</v>
+        <v>2.417958419462091</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.441435570061628</v>
+        <v>-4.603556384647204</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.210871608868217</v>
+        <v>1.146023283033986</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7855452195000325</v>
+        <v>-0.78825408687207</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.516475129506596</v>
+        <v>2.514849809083374</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.423666111130673</v>
+        <v>-4.585786925716248</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.133319084527321</v>
+        <v>1.06847075869309</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7677757605690769</v>
+        <v>-0.7704846279411144</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.442476496951891</v>
+        <v>2.440851176528668</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.336866613351663</v>
+        <v>-4.498987427937239</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.19043937696149</v>
+        <v>1.12559105112726</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7677757605690769</v>
+        <v>-0.7704846279411144</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.464876990274457</v>
+        <v>2.463251669851235</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.237173998622652</v>
+        <v>-4.399294813208227</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.230388824226507</v>
+        <v>1.165540498392277</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6680831458400651</v>
+        <v>-0.6707920132121026</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.524764960485276</v>
+        <v>2.523139640062054</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.305544184946662</v>
+        <v>-4.467664999532238</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.214047672171605</v>
+        <v>1.149199346337375</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6588074468038502</v>
+        <v>-0.6615163141758876</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.541337302381707</v>
+        <v>2.539711981958485</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.184127755320185</v>
+        <v>-4.346248569905761</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.253050952654087</v>
+        <v>1.188202626819857</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6588074468038502</v>
+        <v>-0.6615163141758876</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.531774011013598</v>
+        <v>2.530148690590376</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.215120914648891</v>
+        <v>-4.377241729234466</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.065363253962992</v>
+        <v>1.000514928128762</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6588074468038502</v>
+        <v>-0.6615163141758876</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.356483576053985</v>
+        <v>2.354858255630763</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.407043036771678</v>
+        <v>3.400112244027661</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.756335276128083</v>
+        <v>2.567937243196811</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.060474180603867</v>
+        <v>-4.199771210755308</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.131789179572789</v>
+        <v>0.887672334580941</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6588074468038502</v>
+        <v>-0.6615163141758876</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.361050808045773</v>
+        <v>2.171027454691279</v>
       </c>
     </row>
   </sheetData>
